--- a/artfynd/A 7771-2024 artfynd.xlsx
+++ b/artfynd/A 7771-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115818923</v>
+        <v>338229</v>
       </c>
       <c r="B2" t="n">
-        <v>90885</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92510</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3884</v>
+        <v>1143</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Blekticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Haploporus tuberculosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kungs Barkarö, Vstm</t>
+          <t>Tallholmen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558987</v>
+        <v>559199</v>
       </c>
       <c r="R2" t="n">
-        <v>6591320</v>
+        <v>6591370</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2009-09-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2009-09-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,76 +764,98 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115832758</v>
+        <v>86992170</v>
       </c>
       <c r="B3" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kungs Barkarö, Vstm</t>
+          <t>Tallholmen, Kungs-Barkarö, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559079</v>
+        <v>559198</v>
       </c>
       <c r="R3" t="n">
-        <v>6591394</v>
+        <v>6591345</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,12 +879,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2020-01-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2020-01-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,62 +893,80 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Trädklädd betesmark med ek</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>På liggande granlåga</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies # På liggande granlåga</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115832735</v>
+        <v>115818752</v>
       </c>
       <c r="B4" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558978</v>
+        <v>559003</v>
       </c>
       <c r="R4" t="n">
-        <v>6591527</v>
+        <v>6591339</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,43 +1037,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115832767</v>
+        <v>115818923</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>3884</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1039,13 +1075,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559079</v>
+        <v>558987</v>
       </c>
       <c r="R5" t="n">
-        <v>6591394</v>
+        <v>6591320</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1077,17 +1113,13 @@
           <t>2024-04-08</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spår</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1106,15 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115832790</v>
+        <v>115832767</v>
       </c>
       <c r="B6" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,27 +1149,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1150,13 +1177,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558983</v>
+        <v>559079</v>
       </c>
       <c r="R6" t="n">
-        <v>6591361</v>
+        <v>6591394</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,13 +1215,17 @@
           <t>2024-04-08</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1210,6 +1241,312 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>115832735</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kungs Barkarö, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>558978</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6591527</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kungs-Barkarö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>115832758</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kungs Barkarö, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>559079</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6591394</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kungs-Barkarö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>115832790</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kungs Barkarö, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>558983</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6591361</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kungs-Barkarö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7771-2024 artfynd.xlsx
+++ b/artfynd/A 7771-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/338229</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -933,6 +943,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86992170</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1034,6 +1049,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115818752</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115818923</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1241,6 +1266,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115832767</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115832735</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115832758</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1547,8 +1587,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115832790</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>